--- a/fulls/full_mestre_lf2a_2025.xlsx
+++ b/fulls/full_mestre_lf2a_2025.xlsx
@@ -263,9 +263,9 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Jugadores" displayName="Jugadores" ref="A1:AF144" headerRowCount="1">
-  <autoFilter ref="A1:AF144"/>
-  <tableColumns count="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Jugadores" displayName="Jugadores" ref="A1:AJ144" headerRowCount="1">
+  <autoFilter ref="A1:AJ144"/>
+  <tableColumns count="36">
     <tableColumn id="1" name="Equip"/>
     <tableColumn id="2" name="Jugadora"/>
     <tableColumn id="3" name="PJ"/>
@@ -298,6 +298,10 @@
     <tableColumn id="30" name="%RO real"/>
     <tableColumn id="31" name="%RD est."/>
     <tableColumn id="32" name="%RD real"/>
+    <tableColumn id="33" name="%RO equip a pista"/>
+    <tableColumn id="34" name="Dif. RO pista vs equip"/>
+    <tableColumn id="35" name="%RD equip a pista"/>
+    <tableColumn id="36" name="Dif. RD pista vs equip"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
@@ -654,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -787,65 +791,89 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>des del play-by-play: rebots ofensius/defensius propis i del rival mentre és a pista, només partits amb pbp_ok</t>
+          <t>des del play-by-play: rebots propis / rebots disponibles mentre és a pista; només partits amb pbp_ok</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>%ús</t>
+          <t>%RO / %RD equip a pista</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>possessions de l'equip que acaba la jugadora mentre és a pista</t>
+          <t>rebots capturats per tot l'equip / disponibles mentre ella és a pista; només partits amb pbp_ok</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Quintets/Parelles/Trios</t>
+          <t>Dif. pista vs equip</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>mínims de minuts junts: 20, 100 i 100. ORtg i DRtg per 100 possessions</t>
+          <t>%RO/%RD de l'equip amb ella a pista menys el %RO/%RD de l'equip en tots els seus partits amb pbp_ok</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Zones de tir</t>
+          <t>%ús</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12 zones; els triples s'ajusten perquè quadrin amb l'acta</t>
+          <t>possessions de l'equip que acaba la jugadora mentre és a pista</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Clutch time</t>
+          <t>Quintets/Parelles/Trios</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>últims 5 min del Q4 (o pròrrogues senceres) amb marge &lt;=5 en tot moment; el rellotge s'atura si el marge s'obre</t>
+          <t>mínims de minuts junts: 20, 100 i 100. ORtg i DRtg per 100 possessions</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
+          <t>Zones de tir</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>12 zones; els triples s'ajusten perquè quadrin amb l'acta</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Clutch time</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>últims 5 min del Q4 (o pròrrogues senceres) amb marge &lt;=5 en tot moment; el rellotge s'atura si el marge s'obre</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
           <t>Partits sense play-by-play</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>cap</t>
         </is>
@@ -4200,7 +4228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF144"/>
+  <dimension ref="A1:AJ144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4235,6 +4263,10 @@
     <col width="9" customWidth="1" min="30" max="30"/>
     <col width="9" customWidth="1" min="31" max="31"/>
     <col width="9" customWidth="1" min="32" max="32"/>
+    <col width="9" customWidth="1" min="33" max="33"/>
+    <col width="9" customWidth="1" min="34" max="34"/>
+    <col width="9" customWidth="1" min="35" max="35"/>
+    <col width="9" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -4398,6 +4430,26 @@
           <t>%RD real</t>
         </is>
       </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
+          <t>%RO equip a pista</t>
+        </is>
+      </c>
+      <c r="AH1" s="3" t="inlineStr">
+        <is>
+          <t>Dif. RO pista vs equip</t>
+        </is>
+      </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>%RD equip a pista</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>Dif. RD pista vs equip</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -4492,13 +4544,25 @@
         <v>0.0975</v>
       </c>
       <c r="AD2" s="6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="AE2" s="6" t="n">
         <v>0.3644</v>
       </c>
       <c r="AF2" s="6" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AG2" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AH2" s="6" t="n">
+        <v>-0.0864</v>
+      </c>
+      <c r="AI2" s="6" t="n">
         <v>0.8</v>
+      </c>
+      <c r="AJ2" s="6" t="n">
+        <v>0.0157</v>
       </c>
     </row>
     <row r="3">
@@ -4594,13 +4658,25 @@
         <v>0.0325</v>
       </c>
       <c r="AD3" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.0333</v>
       </c>
       <c r="AE3" s="6" t="n">
         <v>0.2527</v>
       </c>
       <c r="AF3" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG3" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AH3" s="6" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="AI3" s="6" t="n">
         <v>0.8056</v>
+      </c>
+      <c r="AJ3" s="6" t="n">
+        <v>0.0212</v>
       </c>
     </row>
     <row r="4">
@@ -4696,13 +4772,25 @@
         <v>0.145</v>
       </c>
       <c r="AD4" s="6" t="n">
-        <v>0.3704</v>
+        <v>0.1481</v>
       </c>
       <c r="AE4" s="6" t="n">
         <v>0.1876</v>
       </c>
       <c r="AF4" s="6" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AG4" s="6" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="AH4" s="6" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="AI4" s="6" t="n">
         <v>0.7812</v>
+      </c>
+      <c r="AJ4" s="6" t="n">
+        <v>-0.0031</v>
       </c>
     </row>
     <row r="5">
@@ -4798,13 +4886,25 @@
         <v>0.0393</v>
       </c>
       <c r="AD5" s="6" t="n">
-        <v>0.4167</v>
+        <v>0.0417</v>
       </c>
       <c r="AE5" s="6" t="n">
         <v>0.0677</v>
       </c>
       <c r="AF5" s="6" t="n">
+        <v>0.0645</v>
+      </c>
+      <c r="AG5" s="6" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="AH5" s="6" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="AI5" s="6" t="n">
         <v>0.7742</v>
+      </c>
+      <c r="AJ5" s="6" t="n">
+        <v>-0.0101</v>
       </c>
     </row>
     <row r="6">
@@ -4900,13 +5000,25 @@
         <v>0.1566</v>
       </c>
       <c r="AD6" s="6" t="n">
-        <v>0.3846</v>
+        <v>0.1538</v>
       </c>
       <c r="AE6" s="6" t="n">
         <v>0.1689</v>
       </c>
       <c r="AF6" s="6" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="AG6" s="6" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="AH6" s="6" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="AI6" s="6" t="n">
         <v>0.7742</v>
+      </c>
+      <c r="AJ6" s="6" t="n">
+        <v>-0.0101</v>
       </c>
     </row>
     <row r="7">
@@ -5002,13 +5114,25 @@
         <v>0.0896</v>
       </c>
       <c r="AD7" s="6" t="n">
-        <v>0.5</v>
+        <v>0.0769</v>
       </c>
       <c r="AE7" s="6" t="n">
         <v>0.0387</v>
       </c>
       <c r="AF7" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="AG7" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH7" s="6" t="n">
+        <v>0.1136</v>
+      </c>
+      <c r="AI7" s="6" t="n">
         <v>0.7778</v>
+      </c>
+      <c r="AJ7" s="6" t="n">
+        <v>-0.0065</v>
       </c>
     </row>
     <row r="8">
@@ -5104,13 +5228,25 @@
         <v>0</v>
       </c>
       <c r="AD8" s="6" t="n">
-        <v>0.4286</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="6" t="n">
         <v>0.0443</v>
       </c>
       <c r="AF8" s="6" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="AG8" s="6" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="AH8" s="6" t="n">
+        <v>0.0422</v>
+      </c>
+      <c r="AI8" s="6" t="n">
         <v>0.7368</v>
+      </c>
+      <c r="AJ8" s="6" t="n">
+        <v>-0.0475</v>
       </c>
     </row>
     <row r="9">
@@ -5206,13 +5342,25 @@
         <v>0.0536</v>
       </c>
       <c r="AD9" s="6" t="n">
-        <v>0.3684</v>
+        <v>0.0526</v>
       </c>
       <c r="AE9" s="6" t="n">
         <v>0.0463</v>
       </c>
       <c r="AF9" s="6" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AG9" s="6" t="n">
+        <v>0.3684</v>
+      </c>
+      <c r="AH9" s="6" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="AI9" s="6" t="n">
         <v>0.8125</v>
+      </c>
+      <c r="AJ9" s="6" t="n">
+        <v>0.0282</v>
       </c>
     </row>
     <row r="10">
@@ -5308,13 +5456,25 @@
         <v>0</v>
       </c>
       <c r="AD10" s="6" t="n">
-        <v>0.4167</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="6" t="n">
         <v>0.1756</v>
       </c>
       <c r="AF10" s="6" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="AG10" s="6" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="AH10" s="6" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="AI10" s="6" t="n">
         <v>0.8889</v>
+      </c>
+      <c r="AJ10" s="6" t="n">
+        <v>0.1046</v>
       </c>
     </row>
     <row r="11">
@@ -5410,13 +5570,25 @@
         <v>0.104</v>
       </c>
       <c r="AD11" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="AE11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="6" t="n">
+      <c r="AH11" s="6" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="AI11" s="6" t="n">
         <v>0.7143</v>
+      </c>
+      <c r="AJ11" s="6" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -5512,13 +5684,25 @@
         <v>0</v>
       </c>
       <c r="AD12" s="6" t="n">
-        <v>0.303</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="6" t="n">
         <v>0.0891</v>
       </c>
       <c r="AF12" s="6" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="AG12" s="6" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="AH12" s="6" t="n">
+        <v>0.0399</v>
+      </c>
+      <c r="AI12" s="6" t="n">
         <v>0.7714</v>
+      </c>
+      <c r="AJ12" s="6" t="n">
+        <v>-0.0091</v>
       </c>
     </row>
     <row r="13">
@@ -5614,13 +5798,25 @@
         <v>0.0365</v>
       </c>
       <c r="AD13" s="6" t="n">
-        <v>0.2759</v>
+        <v>0.0345</v>
       </c>
       <c r="AE13" s="6" t="n">
         <v>0.0678</v>
       </c>
       <c r="AF13" s="6" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="AG13" s="6" t="n">
+        <v>0.2759</v>
+      </c>
+      <c r="AH13" s="6" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="AI13" s="6" t="n">
         <v>0.7931</v>
+      </c>
+      <c r="AJ13" s="6" t="n">
+        <v>0.0126</v>
       </c>
     </row>
     <row r="14">
@@ -5716,13 +5912,25 @@
         <v>0.0384</v>
       </c>
       <c r="AD14" s="6" t="n">
-        <v>0.3077</v>
+        <v>0.0385</v>
       </c>
       <c r="AE14" s="6" t="n">
         <v>0.1425</v>
       </c>
       <c r="AF14" s="6" t="n">
+        <v>0.1379</v>
+      </c>
+      <c r="AG14" s="6" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AH14" s="6" t="n">
+        <v>0.0445</v>
+      </c>
+      <c r="AI14" s="6" t="n">
         <v>0.8276</v>
+      </c>
+      <c r="AJ14" s="6" t="n">
+        <v>0.0471</v>
       </c>
     </row>
     <row r="15">
@@ -5818,13 +6026,25 @@
         <v>0.083</v>
       </c>
       <c r="AD15" s="6" t="n">
-        <v>0.2727</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="AE15" s="6" t="n">
         <v>0.4615</v>
       </c>
       <c r="AF15" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG15" s="6" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="AH15" s="6" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="AI15" s="6" t="n">
         <v>0.8667</v>
+      </c>
+      <c r="AJ15" s="6" t="n">
+        <v>0.0862</v>
       </c>
     </row>
     <row r="16">
@@ -5920,13 +6140,25 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="AD16" s="6" t="n">
-        <v>0.2222</v>
+        <v>0.0741</v>
       </c>
       <c r="AE16" s="6" t="n">
         <v>0.2016</v>
       </c>
       <c r="AF16" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG16" s="6" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="AH16" s="6" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AI16" s="6" t="n">
         <v>0.76</v>
+      </c>
+      <c r="AJ16" s="6" t="n">
+        <v>-0.0205</v>
       </c>
     </row>
     <row r="17">
@@ -6022,13 +6254,25 @@
         <v>0</v>
       </c>
       <c r="AD17" s="6" t="n">
-        <v>0.2941</v>
+        <v>0</v>
       </c>
       <c r="AE17" s="6" t="n">
         <v>0.08160000000000001</v>
       </c>
       <c r="AF17" s="6" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="AG17" s="6" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="AH17" s="6" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="AI17" s="6" t="n">
         <v>0.7727000000000001</v>
+      </c>
+      <c r="AJ17" s="6" t="n">
+        <v>-0.0078</v>
       </c>
     </row>
     <row r="18">
@@ -6124,13 +6368,25 @@
         <v>0.0455</v>
       </c>
       <c r="AD18" s="6" t="n">
-        <v>0.1579</v>
+        <v>0.0526</v>
       </c>
       <c r="AE18" s="6" t="n">
         <v>0.0844</v>
       </c>
       <c r="AF18" s="6" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AG18" s="6" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="AH18" s="6" t="n">
+        <v>-0.1053</v>
+      </c>
+      <c r="AI18" s="6" t="n">
         <v>0.7391</v>
+      </c>
+      <c r="AJ18" s="6" t="n">
+        <v>-0.0414</v>
       </c>
     </row>
     <row r="19">
@@ -6226,13 +6482,25 @@
         <v>0.2198</v>
       </c>
       <c r="AD19" s="6" t="n">
-        <v>0.2353</v>
+        <v>0.1765</v>
       </c>
       <c r="AE19" s="6" t="n">
         <v>0.1358</v>
       </c>
       <c r="AF19" s="6" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="AG19" s="6" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="AH19" s="6" t="n">
+        <v>-0.0279</v>
+      </c>
+      <c r="AI19" s="6" t="n">
         <v>0.5833</v>
+      </c>
+      <c r="AJ19" s="6" t="n">
+        <v>-0.1972</v>
       </c>
     </row>
     <row r="20">
@@ -6328,13 +6596,25 @@
         <v>0.0796</v>
       </c>
       <c r="AD20" s="6" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="AE20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="6" t="n">
         <v>0.4583</v>
       </c>
-      <c r="AE20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="6" t="n">
+      <c r="AH20" s="6" t="n">
+        <v>0.1028</v>
+      </c>
+      <c r="AI20" s="6" t="n">
         <v>0.7368</v>
+      </c>
+      <c r="AJ20" s="6" t="n">
+        <v>0.0789</v>
       </c>
     </row>
     <row r="21">
@@ -6430,13 +6710,25 @@
         <v>0.0837</v>
       </c>
       <c r="AD21" s="6" t="n">
-        <v>0.3182</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="AE21" s="6" t="n">
         <v>0.0496</v>
       </c>
       <c r="AF21" s="6" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="AG21" s="6" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="AH21" s="6" t="n">
+        <v>-0.0374</v>
+      </c>
+      <c r="AI21" s="6" t="n">
         <v>0.6957</v>
+      </c>
+      <c r="AJ21" s="6" t="n">
+        <v>0.0378</v>
       </c>
     </row>
     <row r="22">
@@ -6532,13 +6824,25 @@
         <v>0.0422</v>
       </c>
       <c r="AD22" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.037</v>
       </c>
       <c r="AE22" s="6" t="n">
         <v>0.1997</v>
       </c>
       <c r="AF22" s="6" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="AG22" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AH22" s="6" t="n">
+        <v>-0.0222</v>
+      </c>
+      <c r="AI22" s="6" t="n">
         <v>0.5909</v>
+      </c>
+      <c r="AJ22" s="6" t="n">
+        <v>-0.067</v>
       </c>
     </row>
     <row r="23">
@@ -6634,13 +6938,25 @@
         <v>0.0886</v>
       </c>
       <c r="AD23" s="6" t="n">
-        <v>0.2609</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AE23" s="6" t="n">
         <v>0.1573</v>
       </c>
       <c r="AF23" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AG23" s="6" t="n">
+        <v>0.2609</v>
+      </c>
+      <c r="AH23" s="6" t="n">
+        <v>-0.09470000000000001</v>
+      </c>
+      <c r="AI23" s="6" t="n">
         <v>0.7</v>
+      </c>
+      <c r="AJ23" s="6" t="n">
+        <v>0.0421</v>
       </c>
     </row>
     <row r="24">
@@ -6736,13 +7052,25 @@
         <v>0.047</v>
       </c>
       <c r="AD24" s="6" t="n">
-        <v>0.3889</v>
+        <v>0.0556</v>
       </c>
       <c r="AE24" s="6" t="n">
         <v>0.1669</v>
       </c>
       <c r="AF24" s="6" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AG24" s="6" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="AH24" s="6" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="AI24" s="6" t="n">
         <v>0.75</v>
+      </c>
+      <c r="AJ24" s="6" t="n">
+        <v>0.0921</v>
       </c>
     </row>
     <row r="25">
@@ -6838,13 +7166,25 @@
         <v>0.1459</v>
       </c>
       <c r="AD25" s="6" t="n">
-        <v>0.36</v>
+        <v>0.12</v>
       </c>
       <c r="AE25" s="6" t="n">
         <v>0.1728</v>
       </c>
       <c r="AF25" s="6" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="AG25" s="6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AH25" s="6" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="AI25" s="6" t="n">
         <v>0.5556</v>
+      </c>
+      <c r="AJ25" s="6" t="n">
+        <v>-0.1023</v>
       </c>
     </row>
     <row r="26">
@@ -6940,13 +7280,25 @@
         <v>0.05</v>
       </c>
       <c r="AD26" s="6" t="n">
-        <v>0.3043</v>
+        <v>0.0435</v>
       </c>
       <c r="AE26" s="6" t="n">
         <v>0.0592</v>
       </c>
       <c r="AF26" s="6" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="AG26" s="6" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AH26" s="6" t="n">
+        <v>-0.0512</v>
+      </c>
+      <c r="AI26" s="6" t="n">
         <v>0.6667</v>
+      </c>
+      <c r="AJ26" s="6" t="n">
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -7042,13 +7394,25 @@
         <v>0.0503</v>
       </c>
       <c r="AD27" s="6" t="n">
-        <v>0.2381</v>
+        <v>0.0476</v>
       </c>
       <c r="AE27" s="6" t="n">
         <v>0.1191</v>
       </c>
       <c r="AF27" s="6" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="AG27" s="6" t="n">
+        <v>0.2381</v>
+      </c>
+      <c r="AH27" s="6" t="n">
+        <v>-0.1175</v>
+      </c>
+      <c r="AI27" s="6" t="n">
         <v>0.5789</v>
+      </c>
+      <c r="AJ27" s="6" t="n">
+        <v>-0.0789</v>
       </c>
     </row>
     <row r="28">
@@ -7144,13 +7508,25 @@
         <v>0.0558</v>
       </c>
       <c r="AD28" s="6" t="n">
-        <v>0.3846</v>
+        <v>0.0769</v>
       </c>
       <c r="AE28" s="6" t="n">
         <v>0.2643</v>
       </c>
       <c r="AF28" s="6" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AG28" s="6" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="AH28" s="6" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="AI28" s="6" t="n">
         <v>0.8571</v>
+      </c>
+      <c r="AJ28" s="6" t="n">
+        <v>0.1992</v>
       </c>
     </row>
     <row r="29">
@@ -7246,13 +7622,25 @@
         <v>0</v>
       </c>
       <c r="AD29" s="6" t="n">
-        <v>0.5881999999999999</v>
+        <v>0</v>
       </c>
       <c r="AE29" s="6" t="n">
         <v>0.1399</v>
       </c>
       <c r="AF29" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG29" s="6" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="AH29" s="6" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="AI29" s="6" t="n">
         <v>0.5</v>
+      </c>
+      <c r="AJ29" s="6" t="n">
+        <v>-0.1579</v>
       </c>
     </row>
     <row r="30">
@@ -7348,13 +7736,25 @@
         <v>0.1852</v>
       </c>
       <c r="AD30" s="6" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="AE30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="6" t="n">
         <v>0.4444</v>
       </c>
-      <c r="AE30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" s="6" t="n">
+      <c r="AH30" s="6" t="n">
+        <v>0.08890000000000001</v>
+      </c>
+      <c r="AI30" s="6" t="n">
         <v>0.375</v>
+      </c>
+      <c r="AJ30" s="6" t="n">
+        <v>-0.2829</v>
       </c>
     </row>
     <row r="31">
@@ -7456,7 +7856,19 @@
         <v>1.017</v>
       </c>
       <c r="AF31" s="6" t="n">
-        <v>1</v>
+        <v>0.6667</v>
+      </c>
+      <c r="AG31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="6" t="n">
+        <v>-0.3556</v>
+      </c>
+      <c r="AI31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ31" s="6" t="n">
+        <v>0.3421</v>
       </c>
     </row>
     <row r="32">
@@ -7558,7 +7970,19 @@
         <v>0.1246</v>
       </c>
       <c r="AF32" s="6" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="AG32" s="6" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="AH32" s="6" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="AI32" s="6" t="n">
         <v>0.6571</v>
+      </c>
+      <c r="AJ32" s="6" t="n">
+        <v>0.0161</v>
       </c>
     </row>
     <row r="33">
@@ -7654,13 +8078,25 @@
         <v>0</v>
       </c>
       <c r="AD33" s="6" t="n">
-        <v>0.0417</v>
+        <v>0</v>
       </c>
       <c r="AE33" s="6" t="n">
         <v>0.1088</v>
       </c>
       <c r="AF33" s="6" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="AG33" s="6" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AH33" s="6" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="AI33" s="6" t="n">
         <v>0.6129</v>
+      </c>
+      <c r="AJ33" s="6" t="n">
+        <v>-0.0281</v>
       </c>
     </row>
     <row r="34">
@@ -7762,7 +8198,19 @@
         <v>0.3039</v>
       </c>
       <c r="AF34" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AG34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="AI34" s="6" t="n">
         <v>0.7083</v>
+      </c>
+      <c r="AJ34" s="6" t="n">
+        <v>0.0673</v>
       </c>
     </row>
     <row r="35">
@@ -7858,13 +8306,25 @@
         <v>0</v>
       </c>
       <c r="AD35" s="6" t="n">
-        <v>0.0435</v>
+        <v>0</v>
       </c>
       <c r="AE35" s="6" t="n">
         <v>0.07820000000000001</v>
       </c>
       <c r="AF35" s="6" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="AG35" s="6" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="AH35" s="6" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="AI35" s="6" t="n">
         <v>0.6667</v>
+      </c>
+      <c r="AJ35" s="6" t="n">
+        <v>0.0256</v>
       </c>
     </row>
     <row r="36">
@@ -7960,13 +8420,25 @@
         <v>0</v>
       </c>
       <c r="AD36" s="6" t="n">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="AE36" s="6" t="n">
         <v>0.0815</v>
       </c>
       <c r="AF36" s="6" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="AG36" s="6" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="AH36" s="6" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="AI36" s="6" t="n">
         <v>0.6153999999999999</v>
+      </c>
+      <c r="AJ36" s="6" t="n">
+        <v>-0.0256</v>
       </c>
     </row>
     <row r="37">
@@ -8068,7 +8540,19 @@
         <v>0.1085</v>
       </c>
       <c r="AF37" s="6" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="AG37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="6" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="AI37" s="6" t="n">
         <v>0.6111</v>
+      </c>
+      <c r="AJ37" s="6" t="n">
+        <v>-0.0299</v>
       </c>
     </row>
     <row r="38">
@@ -8170,7 +8654,19 @@
         <v>0</v>
       </c>
       <c r="AF38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="6" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="AI38" s="6" t="n">
         <v>0.7143</v>
+      </c>
+      <c r="AJ38" s="6" t="n">
+        <v>0.0733</v>
       </c>
     </row>
     <row r="39">
@@ -8272,7 +8768,19 @@
         <v>0</v>
       </c>
       <c r="AF39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="6" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="AI39" s="6" t="n">
         <v>0.75</v>
+      </c>
+      <c r="AJ39" s="6" t="n">
+        <v>0.109</v>
       </c>
     </row>
     <row r="40">
@@ -8368,13 +8876,25 @@
         <v>0</v>
       </c>
       <c r="AD40" s="6" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="AE40" s="6" t="n">
         <v>0.5778</v>
       </c>
       <c r="AF40" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG40" s="6" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="AH40" s="6" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="AI40" s="6" t="n">
         <v>0.5</v>
+      </c>
+      <c r="AJ40" s="6" t="n">
+        <v>-0.141</v>
       </c>
     </row>
     <row r="41">
@@ -8476,7 +8996,19 @@
         <v>0</v>
       </c>
       <c r="AF41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="6" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="AI41" s="6" t="n">
         <v>0.6667</v>
+      </c>
+      <c r="AJ41" s="6" t="n">
+        <v>0.0256</v>
       </c>
     </row>
     <row r="42">
@@ -8578,7 +9110,19 @@
         <v>0</v>
       </c>
       <c r="AF42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="AI42" s="6" t="n">
         <v>0.5714</v>
+      </c>
+      <c r="AJ42" s="6" t="n">
+        <v>-0.0696</v>
       </c>
     </row>
     <row r="43">
@@ -8680,7 +9224,19 @@
         <v>0</v>
       </c>
       <c r="AF43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="6" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="AI43" s="6" t="n">
         <v>0.5</v>
+      </c>
+      <c r="AJ43" s="6" t="n">
+        <v>-0.141</v>
       </c>
     </row>
     <row r="44">
@@ -8776,13 +9332,25 @@
         <v>0.1022</v>
       </c>
       <c r="AD44" s="6" t="n">
-        <v>0.2222</v>
+        <v>0.1111</v>
       </c>
       <c r="AE44" s="6" t="n">
         <v>0.1704</v>
       </c>
       <c r="AF44" s="6" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="AG44" s="6" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="AH44" s="6" t="n">
+        <v>-0.0222</v>
+      </c>
+      <c r="AI44" s="6" t="n">
         <v>0.6875</v>
+      </c>
+      <c r="AJ44" s="6" t="n">
+        <v>-0.0236</v>
       </c>
     </row>
     <row r="45">
@@ -8878,13 +9446,25 @@
         <v>0.0352</v>
       </c>
       <c r="AD45" s="6" t="n">
-        <v>0.3103</v>
+        <v>0.0345</v>
       </c>
       <c r="AE45" s="6" t="n">
         <v>0.0704</v>
       </c>
       <c r="AF45" s="6" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="AG45" s="6" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AH45" s="6" t="n">
+        <v>0.0659</v>
+      </c>
+      <c r="AI45" s="6" t="n">
         <v>0.7407</v>
+      </c>
+      <c r="AJ45" s="6" t="n">
+        <v>0.0296</v>
       </c>
     </row>
     <row r="46">
@@ -8980,13 +9560,25 @@
         <v>0</v>
       </c>
       <c r="AD46" s="6" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
       <c r="AE46" s="6" t="n">
         <v>0.2502</v>
       </c>
       <c r="AF46" s="6" t="n">
+        <v>0.2593</v>
+      </c>
+      <c r="AG46" s="6" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="AH46" s="6" t="n">
+        <v>-0.07779999999999999</v>
+      </c>
+      <c r="AI46" s="6" t="n">
         <v>0.7407</v>
+      </c>
+      <c r="AJ46" s="6" t="n">
+        <v>0.0296</v>
       </c>
     </row>
     <row r="47">
@@ -9082,13 +9674,25 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="AD47" s="6" t="n">
-        <v>0.2692</v>
+        <v>0.0769</v>
       </c>
       <c r="AE47" s="6" t="n">
         <v>0.0365</v>
       </c>
       <c r="AF47" s="6" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="AG47" s="6" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="AH47" s="6" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="AI47" s="6" t="n">
         <v>0.6538</v>
+      </c>
+      <c r="AJ47" s="6" t="n">
+        <v>-0.0573</v>
       </c>
     </row>
     <row r="48">
@@ -9184,13 +9788,25 @@
         <v>0.038</v>
       </c>
       <c r="AD48" s="6" t="n">
-        <v>0.2083</v>
+        <v>0.0417</v>
       </c>
       <c r="AE48" s="6" t="n">
         <v>0.1519</v>
       </c>
       <c r="AF48" s="6" t="n">
+        <v>0.1379</v>
+      </c>
+      <c r="AG48" s="6" t="n">
+        <v>0.2083</v>
+      </c>
+      <c r="AH48" s="6" t="n">
+        <v>-0.0361</v>
+      </c>
+      <c r="AI48" s="6" t="n">
         <v>0.7241</v>
+      </c>
+      <c r="AJ48" s="6" t="n">
+        <v>0.013</v>
       </c>
     </row>
     <row r="49">
@@ -9286,13 +9902,25 @@
         <v>0.0412</v>
       </c>
       <c r="AD49" s="6" t="n">
-        <v>0.3846</v>
+        <v>0.0385</v>
       </c>
       <c r="AE49" s="6" t="n">
         <v>0.2469</v>
       </c>
       <c r="AF49" s="6" t="n">
+        <v>0.2609</v>
+      </c>
+      <c r="AG49" s="6" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="AH49" s="6" t="n">
+        <v>0.1402</v>
+      </c>
+      <c r="AI49" s="6" t="n">
         <v>0.7826</v>
+      </c>
+      <c r="AJ49" s="6" t="n">
+        <v>0.07149999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -9388,13 +10016,25 @@
         <v>0.0862</v>
       </c>
       <c r="AD50" s="6" t="n">
-        <v>0.1667</v>
+        <v>0.0833</v>
       </c>
       <c r="AE50" s="6" t="n">
         <v>0.1293</v>
       </c>
       <c r="AF50" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG50" s="6" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="AH50" s="6" t="n">
+        <v>-0.07779999999999999</v>
+      </c>
+      <c r="AI50" s="6" t="n">
         <v>0.68</v>
+      </c>
+      <c r="AJ50" s="6" t="n">
+        <v>-0.0311</v>
       </c>
     </row>
     <row r="51">
@@ -9490,13 +10130,25 @@
         <v>0.0585</v>
       </c>
       <c r="AD51" s="6" t="n">
-        <v>0.1875</v>
+        <v>0.0625</v>
       </c>
       <c r="AE51" s="6" t="n">
         <v>0.0585</v>
       </c>
       <c r="AF51" s="6" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="AG51" s="6" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AH51" s="6" t="n">
+        <v>-0.0569</v>
+      </c>
+      <c r="AI51" s="6" t="n">
         <v>0.6471</v>
+      </c>
+      <c r="AJ51" s="6" t="n">
+        <v>-0.0641</v>
       </c>
     </row>
     <row r="52">
@@ -9592,13 +10244,25 @@
         <v>0</v>
       </c>
       <c r="AD52" s="6" t="n">
-        <v>0.2105</v>
+        <v>0</v>
       </c>
       <c r="AE52" s="6" t="n">
         <v>0.1774</v>
       </c>
       <c r="AF52" s="6" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AG52" s="6" t="n">
+        <v>0.2105</v>
+      </c>
+      <c r="AH52" s="6" t="n">
+        <v>-0.0339</v>
+      </c>
+      <c r="AI52" s="6" t="n">
         <v>0.75</v>
+      </c>
+      <c r="AJ52" s="6" t="n">
+        <v>0.0389</v>
       </c>
     </row>
     <row r="53">
@@ -9694,13 +10358,25 @@
         <v>0</v>
       </c>
       <c r="AD53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" s="6" t="n">
+      <c r="AH53" s="6" t="n">
+        <v>0.2556</v>
+      </c>
+      <c r="AI53" s="6" t="n">
         <v>0.6667</v>
+      </c>
+      <c r="AJ53" s="6" t="n">
+        <v>-0.0444</v>
       </c>
     </row>
     <row r="54">
@@ -9796,13 +10472,25 @@
         <v>0.07729999999999999</v>
       </c>
       <c r="AD54" s="6" t="n">
-        <v>0.225</v>
+        <v>0.075</v>
       </c>
       <c r="AE54" s="6" t="n">
         <v>0.2986</v>
       </c>
       <c r="AF54" s="6" t="n">
+        <v>0.2703</v>
+      </c>
+      <c r="AG54" s="6" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="AH54" s="6" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="AI54" s="6" t="n">
         <v>0.6216</v>
+      </c>
+      <c r="AJ54" s="6" t="n">
+        <v>0.008</v>
       </c>
     </row>
     <row r="55">
@@ -9898,13 +10586,25 @@
         <v>0.0309</v>
       </c>
       <c r="AD55" s="6" t="n">
-        <v>0.2</v>
+        <v>0.0333</v>
       </c>
       <c r="AE55" s="6" t="n">
         <v>0.2151</v>
       </c>
       <c r="AF55" s="6" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="AG55" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH55" s="6" t="n">
+        <v>-0.0157</v>
+      </c>
+      <c r="AI55" s="6" t="n">
         <v>0.5758</v>
+      </c>
+      <c r="AJ55" s="6" t="n">
+        <v>-0.0379</v>
       </c>
     </row>
     <row r="56">
@@ -10000,13 +10700,25 @@
         <v>0.0653</v>
       </c>
       <c r="AD56" s="6" t="n">
-        <v>0.1818</v>
+        <v>0.0606</v>
       </c>
       <c r="AE56" s="6" t="n">
         <v>0.1135</v>
       </c>
       <c r="AF56" s="6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AG56" s="6" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="AH56" s="6" t="n">
+        <v>-0.0339</v>
+      </c>
+      <c r="AI56" s="6" t="n">
         <v>0.6667</v>
+      </c>
+      <c r="AJ56" s="6" t="n">
+        <v>0.053</v>
       </c>
     </row>
     <row r="57">
@@ -10102,13 +10814,25 @@
         <v>0</v>
       </c>
       <c r="AD57" s="6" t="n">
-        <v>0.1538</v>
+        <v>0</v>
       </c>
       <c r="AE57" s="6" t="n">
         <v>0.0388</v>
       </c>
       <c r="AF57" s="6" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="AG57" s="6" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="AH57" s="6" t="n">
+        <v>-0.0618</v>
+      </c>
+      <c r="AI57" s="6" t="n">
         <v>0.6071</v>
+      </c>
+      <c r="AJ57" s="6" t="n">
+        <v>-0.0065</v>
       </c>
     </row>
     <row r="58">
@@ -10204,13 +10928,25 @@
         <v>0</v>
       </c>
       <c r="AD58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="6" t="n">
         <v>0.1667</v>
       </c>
-      <c r="AE58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF58" s="6" t="n">
+      <c r="AH58" s="6" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="AI58" s="6" t="n">
         <v>0.5714</v>
+      </c>
+      <c r="AJ58" s="6" t="n">
+        <v>-0.0422</v>
       </c>
     </row>
     <row r="59">
@@ -10306,13 +11042,25 @@
         <v>0.1188</v>
       </c>
       <c r="AD59" s="6" t="n">
-        <v>0.2917</v>
+        <v>0.125</v>
       </c>
       <c r="AE59" s="6" t="n">
         <v>0.09180000000000001</v>
       </c>
       <c r="AF59" s="6" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="AG59" s="6" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="AH59" s="6" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="AI59" s="6" t="n">
         <v>0.6296</v>
+      </c>
+      <c r="AJ59" s="6" t="n">
+        <v>0.016</v>
       </c>
     </row>
     <row r="60">
@@ -10408,13 +11156,25 @@
         <v>0.0459</v>
       </c>
       <c r="AD60" s="6" t="n">
-        <v>0.2083</v>
+        <v>0.0417</v>
       </c>
       <c r="AE60" s="6" t="n">
         <v>0.0532</v>
       </c>
       <c r="AF60" s="6" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="AG60" s="6" t="n">
+        <v>0.2083</v>
+      </c>
+      <c r="AH60" s="6" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="AI60" s="6" t="n">
         <v>0.6153999999999999</v>
+      </c>
+      <c r="AJ60" s="6" t="n">
+        <v>0.0017</v>
       </c>
     </row>
     <row r="61">
@@ -10510,13 +11270,25 @@
         <v>0.062</v>
       </c>
       <c r="AD61" s="6" t="n">
-        <v>0.2667</v>
+        <v>0.0667</v>
       </c>
       <c r="AE61" s="6" t="n">
         <v>0.07190000000000001</v>
       </c>
       <c r="AF61" s="6" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AG61" s="6" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="AH61" s="6" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="AI61" s="6" t="n">
         <v>0.625</v>
+      </c>
+      <c r="AJ61" s="6" t="n">
+        <v>0.0114</v>
       </c>
     </row>
     <row r="62">
@@ -10612,13 +11384,25 @@
         <v>0</v>
       </c>
       <c r="AD62" s="6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AE62" s="6" t="n">
         <v>0.1474</v>
       </c>
       <c r="AF62" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG62" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH62" s="6" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="AI62" s="6" t="n">
         <v>0.625</v>
+      </c>
+      <c r="AJ62" s="6" t="n">
+        <v>0.0114</v>
       </c>
     </row>
     <row r="63">
@@ -10714,13 +11498,25 @@
         <v>0</v>
       </c>
       <c r="AD63" s="6" t="n">
-        <v>0.2941</v>
+        <v>0</v>
       </c>
       <c r="AE63" s="6" t="n">
         <v>0.0767</v>
       </c>
       <c r="AF63" s="6" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="AG63" s="6" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="AH63" s="6" t="n">
+        <v>0.0784</v>
+      </c>
+      <c r="AI63" s="6" t="n">
         <v>0.6153999999999999</v>
+      </c>
+      <c r="AJ63" s="6" t="n">
+        <v>0.0017</v>
       </c>
     </row>
     <row r="64">
@@ -10816,13 +11612,25 @@
         <v>0.0893</v>
       </c>
       <c r="AD64" s="6" t="n">
-        <v>0.375</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="AE64" s="6" t="n">
         <v>0.1799</v>
       </c>
       <c r="AF64" s="6" t="n">
+        <v>0.1892</v>
+      </c>
+      <c r="AG64" s="6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AH64" s="6" t="n">
+        <v>0.0329</v>
+      </c>
+      <c r="AI64" s="6" t="n">
         <v>0.6486</v>
+      </c>
+      <c r="AJ64" s="6" t="n">
+        <v>0.035</v>
       </c>
     </row>
     <row r="65">
@@ -10918,13 +11726,25 @@
         <v>0.0329</v>
       </c>
       <c r="AD65" s="6" t="n">
-        <v>0.4062</v>
+        <v>0.0312</v>
       </c>
       <c r="AE65" s="6" t="n">
         <v>0.0852</v>
       </c>
       <c r="AF65" s="6" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="AG65" s="6" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="AH65" s="6" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="AI65" s="6" t="n">
         <v>0.6286</v>
+      </c>
+      <c r="AJ65" s="6" t="n">
+        <v>0.0149</v>
       </c>
     </row>
     <row r="66">
@@ -11020,13 +11840,25 @@
         <v>0.0677</v>
       </c>
       <c r="AD66" s="6" t="n">
-        <v>0.3667</v>
+        <v>0.0667</v>
       </c>
       <c r="AE66" s="6" t="n">
         <v>0.1462</v>
       </c>
       <c r="AF66" s="6" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="AG66" s="6" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="AH66" s="6" t="n">
+        <v>0.0246</v>
+      </c>
+      <c r="AI66" s="6" t="n">
         <v>0.625</v>
+      </c>
+      <c r="AJ66" s="6" t="n">
+        <v>0.0114</v>
       </c>
     </row>
     <row r="67">
@@ -11122,13 +11954,25 @@
         <v>0</v>
       </c>
       <c r="AD67" s="6" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AE67" s="6" t="n">
         <v>0.09420000000000001</v>
       </c>
       <c r="AF67" s="6" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="AG67" s="6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AH67" s="6" t="n">
+        <v>-0.0621</v>
+      </c>
+      <c r="AI67" s="6" t="n">
         <v>0.6207</v>
+      </c>
+      <c r="AJ67" s="6" t="n">
+        <v>0.0071</v>
       </c>
     </row>
     <row r="68">
@@ -11224,13 +12068,25 @@
         <v>0</v>
       </c>
       <c r="AD68" s="6" t="n">
-        <v>0.3462</v>
+        <v>0</v>
       </c>
       <c r="AE68" s="6" t="n">
         <v>0.133</v>
       </c>
       <c r="AF68" s="6" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="AG68" s="6" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AH68" s="6" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="AI68" s="6" t="n">
         <v>0.5881999999999999</v>
+      </c>
+      <c r="AJ68" s="6" t="n">
+        <v>-0.0254</v>
       </c>
     </row>
     <row r="69">
@@ -11326,13 +12182,25 @@
         <v>0.1973</v>
       </c>
       <c r="AD69" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.2083</v>
       </c>
       <c r="AE69" s="6" t="n">
         <v>0.06809999999999999</v>
       </c>
       <c r="AF69" s="6" t="n">
+        <v>0.0645</v>
+      </c>
+      <c r="AG69" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AH69" s="6" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="AI69" s="6" t="n">
         <v>0.6129</v>
+      </c>
+      <c r="AJ69" s="6" t="n">
+        <v>-0.0007</v>
       </c>
     </row>
     <row r="70">
@@ -11428,13 +12296,25 @@
         <v>0.118</v>
       </c>
       <c r="AD70" s="6" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="AE70" s="6" t="n">
         <v>0.3057</v>
       </c>
       <c r="AF70" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG70" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH70" s="6" t="n">
+        <v>-0.0921</v>
+      </c>
+      <c r="AI70" s="6" t="n">
         <v>0.5833</v>
+      </c>
+      <c r="AJ70" s="6" t="n">
+        <v>-0.0303</v>
       </c>
     </row>
     <row r="71">
@@ -11530,13 +12410,25 @@
         <v>0.1292</v>
       </c>
       <c r="AD71" s="6" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="AE71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="6" t="n">
         <v>0.2727</v>
       </c>
-      <c r="AE71" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF71" s="6" t="n">
+      <c r="AH71" s="6" t="n">
+        <v>-0.0694</v>
+      </c>
+      <c r="AI71" s="6" t="n">
         <v>0.5</v>
+      </c>
+      <c r="AJ71" s="6" t="n">
+        <v>-0.1136</v>
       </c>
     </row>
     <row r="72">
@@ -11638,6 +12530,14 @@
         <v>0</v>
       </c>
       <c r="AF72" s="6" t="n"/>
+      <c r="AG72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" s="6" t="n">
+        <v>-0.3421</v>
+      </c>
+      <c r="AI72" s="6" t="n"/>
+      <c r="AJ72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -11732,13 +12632,25 @@
         <v>0</v>
       </c>
       <c r="AD73" s="6" t="n">
-        <v>0.2258</v>
+        <v>0</v>
       </c>
       <c r="AE73" s="6" t="n">
         <v>0.2168</v>
       </c>
       <c r="AF73" s="6" t="n">
+        <v>0.2121</v>
+      </c>
+      <c r="AG73" s="6" t="n">
+        <v>0.2258</v>
+      </c>
+      <c r="AH73" s="6" t="n">
+        <v>-0.0599</v>
+      </c>
+      <c r="AI73" s="6" t="n">
         <v>0.7272999999999999</v>
+      </c>
+      <c r="AJ73" s="6" t="n">
+        <v>0.013</v>
       </c>
     </row>
     <row r="74">
@@ -11834,13 +12746,25 @@
         <v>0</v>
       </c>
       <c r="AD74" s="6" t="n">
-        <v>0.2963</v>
+        <v>0</v>
       </c>
       <c r="AE74" s="6" t="n">
         <v>0.0379</v>
       </c>
       <c r="AF74" s="6" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AG74" s="6" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="AH74" s="6" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="AI74" s="6" t="n">
         <v>0.7917</v>
+      </c>
+      <c r="AJ74" s="6" t="n">
+        <v>0.0774</v>
       </c>
     </row>
     <row r="75">
@@ -11936,13 +12860,25 @@
         <v>0.0775</v>
       </c>
       <c r="AD75" s="6" t="n">
-        <v>0.2692</v>
+        <v>0.0769</v>
       </c>
       <c r="AE75" s="6" t="n">
         <v>0.1551</v>
       </c>
       <c r="AF75" s="6" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="AG75" s="6" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="AH75" s="6" t="n">
+        <v>-0.0165</v>
+      </c>
+      <c r="AI75" s="6" t="n">
         <v>0.6923</v>
+      </c>
+      <c r="AJ75" s="6" t="n">
+        <v>-0.022</v>
       </c>
     </row>
     <row r="76">
@@ -12038,13 +12974,25 @@
         <v>0.0896</v>
       </c>
       <c r="AD76" s="6" t="n">
-        <v>0.3043</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AE76" s="6" t="n">
         <v>0.1791</v>
       </c>
       <c r="AF76" s="6" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="AG76" s="6" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AH76" s="6" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="AI76" s="6" t="n">
         <v>0.5833</v>
+      </c>
+      <c r="AJ76" s="6" t="n">
+        <v>-0.131</v>
       </c>
     </row>
     <row r="77">
@@ -12144,6 +13092,10 @@
         <v>0.1126</v>
       </c>
       <c r="AF77" s="6" t="n"/>
+      <c r="AG77" s="6" t="n"/>
+      <c r="AH77" s="6" t="n"/>
+      <c r="AI77" s="6" t="n"/>
+      <c r="AJ77" s="6" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -12238,13 +13190,25 @@
         <v>0.1435</v>
       </c>
       <c r="AD78" s="6" t="n">
-        <v>0.3158</v>
+        <v>0.1053</v>
       </c>
       <c r="AE78" s="6" t="n">
         <v>0.0717</v>
       </c>
       <c r="AF78" s="6" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="AG78" s="6" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="AH78" s="6" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="AI78" s="6" t="n">
         <v>0.6923</v>
+      </c>
+      <c r="AJ78" s="6" t="n">
+        <v>-0.022</v>
       </c>
     </row>
     <row r="79">
@@ -12340,13 +13304,25 @@
         <v>0</v>
       </c>
       <c r="AD79" s="6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AE79" s="6" t="n">
         <v>0.1123</v>
       </c>
       <c r="AF79" s="6" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="AG79" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH79" s="6" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="AI79" s="6" t="n">
         <v>0.4545</v>
+      </c>
+      <c r="AJ79" s="6" t="n">
+        <v>-0.2597</v>
       </c>
     </row>
     <row r="80">
@@ -12448,7 +13424,19 @@
         <v>0.2577</v>
       </c>
       <c r="AF80" s="6" t="n">
-        <v>1</v>
+        <v>0.25</v>
+      </c>
+      <c r="AG80" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="6" t="n">
+        <v>-0.2857</v>
+      </c>
+      <c r="AI80" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ80" s="6" t="n">
+        <v>0.2857</v>
       </c>
     </row>
     <row r="81">
@@ -12544,13 +13532,25 @@
         <v>0.1551</v>
       </c>
       <c r="AD81" s="6" t="n">
-        <v>0.5</v>
+        <v>0.1667</v>
       </c>
       <c r="AE81" s="6" t="n">
         <v>0.3101</v>
       </c>
       <c r="AF81" s="6" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="AG81" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH81" s="6" t="n">
+        <v>0.2143</v>
+      </c>
+      <c r="AI81" s="6" t="n">
         <v>0.4444</v>
+      </c>
+      <c r="AJ81" s="6" t="n">
+        <v>-0.2698</v>
       </c>
     </row>
     <row r="82">
@@ -12646,13 +13646,25 @@
         <v>0.1572</v>
       </c>
       <c r="AD82" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.1111</v>
       </c>
       <c r="AE82" s="6" t="n">
         <v>0.1572</v>
       </c>
       <c r="AF82" s="6" t="n">
-        <v>1</v>
+        <v>0.2</v>
+      </c>
+      <c r="AG82" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AH82" s="6" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="AI82" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ82" s="6" t="n">
+        <v>0.2857</v>
       </c>
     </row>
     <row r="83">
@@ -12748,13 +13760,25 @@
         <v>0</v>
       </c>
       <c r="AD83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="AE83" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF83" s="6" t="n">
-        <v>1</v>
+      <c r="AH83" s="6" t="n">
+        <v>-0.0857</v>
+      </c>
+      <c r="AI83" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ83" s="6" t="n">
+        <v>0.2857</v>
       </c>
     </row>
     <row r="84">
@@ -12850,13 +13874,25 @@
         <v>0</v>
       </c>
       <c r="AD84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="6" t="n">
         <v>0.25</v>
       </c>
-      <c r="AE84" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF84" s="6" t="n">
-        <v>1</v>
+      <c r="AH84" s="6" t="n">
+        <v>-0.0357</v>
+      </c>
+      <c r="AI84" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ84" s="6" t="n">
+        <v>0.2857</v>
       </c>
     </row>
     <row r="85">
@@ -12952,13 +13988,25 @@
         <v>0</v>
       </c>
       <c r="AD85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="6" t="n">
         <v>0.2308</v>
       </c>
-      <c r="AE85" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF85" s="6" t="n">
+      <c r="AH85" s="6" t="n">
+        <v>-0.0549</v>
+      </c>
+      <c r="AI85" s="6" t="n">
         <v>0.8235</v>
+      </c>
+      <c r="AJ85" s="6" t="n">
+        <v>0.1092</v>
       </c>
     </row>
     <row r="86">
@@ -13054,13 +14102,25 @@
         <v>0</v>
       </c>
       <c r="AD86" s="6" t="n">
-        <v>0.3077</v>
+        <v>0</v>
       </c>
       <c r="AE86" s="6" t="n">
         <v>0.1348</v>
       </c>
       <c r="AF86" s="6" t="n">
+        <v>0.1154</v>
+      </c>
+      <c r="AG86" s="6" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AH86" s="6" t="n">
+        <v>-0.07870000000000001</v>
+      </c>
+      <c r="AI86" s="6" t="n">
         <v>0.6153999999999999</v>
+      </c>
+      <c r="AJ86" s="6" t="n">
+        <v>-0.0425</v>
       </c>
     </row>
     <row r="87">
@@ -13156,13 +14216,25 @@
         <v>0.1578</v>
       </c>
       <c r="AD87" s="6" t="n">
-        <v>0.4615</v>
+        <v>0.1538</v>
       </c>
       <c r="AE87" s="6" t="n">
         <v>0.0457</v>
       </c>
       <c r="AF87" s="6" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="AG87" s="6" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="AH87" s="6" t="n">
+        <v>0.0752</v>
+      </c>
+      <c r="AI87" s="6" t="n">
         <v>0.7143</v>
+      </c>
+      <c r="AJ87" s="6" t="n">
+        <v>0.0564</v>
       </c>
     </row>
     <row r="88">
@@ -13258,13 +14330,25 @@
         <v>0.1287</v>
       </c>
       <c r="AD88" s="6" t="n">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
       <c r="AE88" s="6" t="n">
         <v>0.2483</v>
       </c>
       <c r="AF88" s="6" t="n">
+        <v>0.1923</v>
+      </c>
+      <c r="AG88" s="6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AH88" s="6" t="n">
+        <v>-0.0664</v>
+      </c>
+      <c r="AI88" s="6" t="n">
         <v>0.6153999999999999</v>
+      </c>
+      <c r="AJ88" s="6" t="n">
+        <v>-0.0425</v>
       </c>
     </row>
     <row r="89">
@@ -13360,13 +14444,25 @@
         <v>0.0458</v>
       </c>
       <c r="AD89" s="6" t="n">
-        <v>0.4444</v>
+        <v>0.0556</v>
       </c>
       <c r="AE89" s="6" t="n">
         <v>0.106</v>
       </c>
       <c r="AF89" s="6" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="AG89" s="6" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="AH89" s="6" t="n">
+        <v>0.0581</v>
+      </c>
+      <c r="AI89" s="6" t="n">
         <v>0.6471</v>
+      </c>
+      <c r="AJ89" s="6" t="n">
+        <v>-0.0108</v>
       </c>
     </row>
     <row r="90">
@@ -13462,13 +14558,25 @@
         <v>0.09180000000000001</v>
       </c>
       <c r="AD90" s="6" t="n">
-        <v>0.4737</v>
+        <v>0.1053</v>
       </c>
       <c r="AE90" s="6" t="n">
         <v>0.0532</v>
       </c>
       <c r="AF90" s="6" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="AG90" s="6" t="n">
+        <v>0.4737</v>
+      </c>
+      <c r="AH90" s="6" t="n">
+        <v>0.0873</v>
+      </c>
+      <c r="AI90" s="6" t="n">
         <v>0.6667</v>
+      </c>
+      <c r="AJ90" s="6" t="n">
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -13564,13 +14672,25 @@
         <v>0.0464</v>
       </c>
       <c r="AD91" s="6" t="n">
-        <v>0.4211</v>
+        <v>0.0526</v>
       </c>
       <c r="AE91" s="6" t="n">
         <v>0.1075</v>
       </c>
       <c r="AF91" s="6" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="AG91" s="6" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="AH91" s="6" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="AI91" s="6" t="n">
         <v>0.6111</v>
+      </c>
+      <c r="AJ91" s="6" t="n">
+        <v>-0.0468</v>
       </c>
     </row>
     <row r="92">
@@ -13666,13 +14786,25 @@
         <v>0</v>
       </c>
       <c r="AD92" s="6" t="n">
-        <v>0.3043</v>
+        <v>0</v>
       </c>
       <c r="AE92" s="6" t="n">
         <v>0.2249</v>
       </c>
       <c r="AF92" s="6" t="n">
+        <v>0.2105</v>
+      </c>
+      <c r="AG92" s="6" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AH92" s="6" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="AI92" s="6" t="n">
         <v>0.6842</v>
+      </c>
+      <c r="AJ92" s="6" t="n">
+        <v>0.0263</v>
       </c>
     </row>
     <row r="93">
@@ -13768,13 +14900,25 @@
         <v>0.098</v>
       </c>
       <c r="AD93" s="6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="AE93" s="6" t="n">
         <v>0.1702</v>
       </c>
       <c r="AF93" s="6" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="AG93" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AH93" s="6" t="n">
+        <v>-0.0864</v>
+      </c>
+      <c r="AI93" s="6" t="n">
         <v>0.619</v>
+      </c>
+      <c r="AJ93" s="6" t="n">
+        <v>-0.0388</v>
       </c>
     </row>
     <row r="94">
@@ -13870,13 +15014,25 @@
         <v>0.2117</v>
       </c>
       <c r="AD94" s="6" t="n">
-        <v>0.4211</v>
+        <v>0.2105</v>
       </c>
       <c r="AE94" s="6" t="n">
         <v>0.1225</v>
       </c>
       <c r="AF94" s="6" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="AG94" s="6" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="AH94" s="6" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="AI94" s="6" t="n">
         <v>0.8182</v>
+      </c>
+      <c r="AJ94" s="6" t="n">
+        <v>0.1603</v>
       </c>
     </row>
     <row r="95">
@@ -13972,13 +15128,25 @@
         <v>0</v>
       </c>
       <c r="AD95" s="6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AE95" s="6" t="n">
         <v>0.1383</v>
       </c>
       <c r="AF95" s="6" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="AG95" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH95" s="6" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="AI95" s="6" t="n">
         <v>0.6923</v>
+      </c>
+      <c r="AJ95" s="6" t="n">
+        <v>0.0344</v>
       </c>
     </row>
     <row r="96">
@@ -14074,13 +15242,25 @@
         <v>0</v>
       </c>
       <c r="AD96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="AE96" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF96" s="6" t="n">
+      <c r="AH96" s="6" t="n">
+        <v>0.2136</v>
+      </c>
+      <c r="AI96" s="6" t="n">
         <v>0.6667</v>
+      </c>
+      <c r="AJ96" s="6" t="n">
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -14180,6 +15360,10 @@
         <v>0</v>
       </c>
       <c r="AF97" s="6" t="n"/>
+      <c r="AG97" s="6" t="n"/>
+      <c r="AH97" s="6" t="n"/>
+      <c r="AI97" s="6" t="n"/>
+      <c r="AJ97" s="6" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -14274,13 +15458,25 @@
         <v>0.0326</v>
       </c>
       <c r="AD98" s="6" t="n">
-        <v>0.2812</v>
+        <v>0.0312</v>
       </c>
       <c r="AE98" s="6" t="n">
         <v>0.1303</v>
       </c>
       <c r="AF98" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AG98" s="6" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="AH98" s="6" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="AI98" s="6" t="n">
         <v>0.7419</v>
+      </c>
+      <c r="AJ98" s="6" t="n">
+        <v>-0.0136</v>
       </c>
     </row>
     <row r="99">
@@ -14376,13 +15572,25 @@
         <v>0.1315</v>
       </c>
       <c r="AD99" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.1333</v>
       </c>
       <c r="AE99" s="6" t="n">
         <v>0.296</v>
       </c>
       <c r="AF99" s="6" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="AG99" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AH99" s="6" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="AI99" s="6" t="n">
         <v>0.8387</v>
+      </c>
+      <c r="AJ99" s="6" t="n">
+        <v>0.0832</v>
       </c>
     </row>
     <row r="100">
@@ -14478,13 +15686,25 @@
         <v>0.0775</v>
       </c>
       <c r="AD100" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.0833</v>
       </c>
       <c r="AE100" s="6" t="n">
         <v>0.1549</v>
       </c>
       <c r="AF100" s="6" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="AG100" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AH100" s="6" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="AI100" s="6" t="n">
         <v>0.7727000000000001</v>
+      </c>
+      <c r="AJ100" s="6" t="n">
+        <v>0.0172</v>
       </c>
     </row>
     <row r="101">
@@ -14580,13 +15800,25 @@
         <v>0</v>
       </c>
       <c r="AD101" s="6" t="n">
-        <v>0.2609</v>
+        <v>0</v>
       </c>
       <c r="AE101" s="6" t="n">
         <v>0.1271</v>
       </c>
       <c r="AF101" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG101" s="6" t="n">
+        <v>0.2609</v>
+      </c>
+      <c r="AH101" s="6" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="AI101" s="6" t="n">
         <v>0.8</v>
+      </c>
+      <c r="AJ101" s="6" t="n">
+        <v>0.0444</v>
       </c>
     </row>
     <row r="102">
@@ -14682,13 +15914,25 @@
         <v>0.0424</v>
       </c>
       <c r="AD102" s="6" t="n">
-        <v>0.1739</v>
+        <v>0.0435</v>
       </c>
       <c r="AE102" s="6" t="n">
         <v>0.1271</v>
       </c>
       <c r="AF102" s="6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AG102" s="6" t="n">
+        <v>0.1739</v>
+      </c>
+      <c r="AH102" s="6" t="n">
+        <v>-0.115</v>
+      </c>
+      <c r="AI102" s="6" t="n">
         <v>0.75</v>
+      </c>
+      <c r="AJ102" s="6" t="n">
+        <v>-0.0056</v>
       </c>
     </row>
     <row r="103">
@@ -14784,13 +16028,25 @@
         <v>0.0445</v>
       </c>
       <c r="AD103" s="6" t="n">
-        <v>0.2727</v>
+        <v>0.0455</v>
       </c>
       <c r="AE103" s="6" t="n">
         <v>0.089</v>
       </c>
       <c r="AF103" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AG103" s="6" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="AH103" s="6" t="n">
+        <v>-0.0162</v>
+      </c>
+      <c r="AI103" s="6" t="n">
         <v>0.76</v>
+      </c>
+      <c r="AJ103" s="6" t="n">
+        <v>0.0044</v>
       </c>
     </row>
     <row r="104">
@@ -14886,13 +16142,25 @@
         <v>0</v>
       </c>
       <c r="AD104" s="6" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="AE104" s="6" t="n">
         <v>0.0992</v>
       </c>
       <c r="AF104" s="6" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="AG104" s="6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AH104" s="6" t="n">
+        <v>0.0711</v>
+      </c>
+      <c r="AI104" s="6" t="n">
         <v>0.7778</v>
+      </c>
+      <c r="AJ104" s="6" t="n">
+        <v>0.0222</v>
       </c>
     </row>
     <row r="105">
@@ -14988,13 +16256,25 @@
         <v>0.1018</v>
       </c>
       <c r="AD105" s="6" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="AE105" s="6" t="n">
         <v>0.2035</v>
       </c>
       <c r="AF105" s="6" t="n">
+        <v>0.2105</v>
+      </c>
+      <c r="AG105" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AH105" s="6" t="n">
+        <v>-0.1389</v>
+      </c>
+      <c r="AI105" s="6" t="n">
         <v>0.5789</v>
+      </c>
+      <c r="AJ105" s="6" t="n">
+        <v>-0.1766</v>
       </c>
     </row>
     <row r="106">
@@ -15090,13 +16370,25 @@
         <v>0</v>
       </c>
       <c r="AD106" s="6" t="n">
-        <v>0.2667</v>
+        <v>0</v>
       </c>
       <c r="AE106" s="6" t="n">
         <v>0.1706</v>
       </c>
       <c r="AF106" s="6" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="AG106" s="6" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="AH106" s="6" t="n">
+        <v>-0.0222</v>
+      </c>
+      <c r="AI106" s="6" t="n">
         <v>0.7368</v>
+      </c>
+      <c r="AJ106" s="6" t="n">
+        <v>-0.0187</v>
       </c>
     </row>
     <row r="107">
@@ -15192,13 +16484,25 @@
         <v>0.1818</v>
       </c>
       <c r="AD107" s="6" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="AE107" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF107" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG107" s="6" t="n">
         <v>0.5455</v>
       </c>
-      <c r="AE107" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF107" s="6" t="n">
+      <c r="AH107" s="6" t="n">
+        <v>0.2566</v>
+      </c>
+      <c r="AI107" s="6" t="n">
         <v>0.7272999999999999</v>
+      </c>
+      <c r="AJ107" s="6" t="n">
+        <v>-0.0283</v>
       </c>
     </row>
     <row r="108">
@@ -15294,13 +16598,25 @@
         <v>0</v>
       </c>
       <c r="AD108" s="6" t="n">
-        <v>0.3103</v>
+        <v>0</v>
       </c>
       <c r="AE108" s="6" t="n">
         <v>0.104</v>
       </c>
       <c r="AF108" s="6" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="AG108" s="6" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AH108" s="6" t="n">
+        <v>0.0246</v>
+      </c>
+      <c r="AI108" s="6" t="n">
         <v>0.6897</v>
+      </c>
+      <c r="AJ108" s="6" t="n">
+        <v>-0.0246</v>
       </c>
     </row>
     <row r="109">
@@ -15396,13 +16712,25 @@
         <v>0.0355</v>
       </c>
       <c r="AD109" s="6" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="AE109" s="6" t="n">
         <v>0.1419</v>
       </c>
       <c r="AF109" s="6" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="AG109" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH109" s="6" t="n">
+        <v>-0.0857</v>
+      </c>
+      <c r="AI109" s="6" t="n">
         <v>0.75</v>
+      </c>
+      <c r="AJ109" s="6" t="n">
+        <v>0.0357</v>
       </c>
     </row>
     <row r="110">
@@ -15498,13 +16826,25 @@
         <v>0.1516</v>
       </c>
       <c r="AD110" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.1481</v>
       </c>
       <c r="AE110" s="6" t="n">
         <v>0.1516</v>
       </c>
       <c r="AF110" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AG110" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AH110" s="6" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="AI110" s="6" t="n">
         <v>0.68</v>
+      </c>
+      <c r="AJ110" s="6" t="n">
+        <v>-0.0343</v>
       </c>
     </row>
     <row r="111">
@@ -15600,13 +16940,25 @@
         <v>0.0775</v>
       </c>
       <c r="AD111" s="6" t="n">
-        <v>0.2857</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="AE111" s="6" t="n">
         <v>0.2324</v>
       </c>
       <c r="AF111" s="6" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="AG111" s="6" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AH111" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="6" t="n">
         <v>0.7692</v>
+      </c>
+      <c r="AJ111" s="6" t="n">
+        <v>0.0549</v>
       </c>
     </row>
     <row r="112">
@@ -15702,13 +17054,25 @@
         <v>0.0506</v>
       </c>
       <c r="AD112" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AE112" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF112" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG112" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="AE112" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF112" s="6" t="n">
+      <c r="AH112" s="6" t="n">
+        <v>-0.1357</v>
+      </c>
+      <c r="AI112" s="6" t="n">
         <v>0.6</v>
+      </c>
+      <c r="AJ112" s="6" t="n">
+        <v>-0.1143</v>
       </c>
     </row>
     <row r="113">
@@ -15804,13 +17168,25 @@
         <v>0.0539</v>
       </c>
       <c r="AD113" s="6" t="n">
-        <v>0.2143</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="AE113" s="6" t="n">
         <v>0.2695</v>
       </c>
       <c r="AF113" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG113" s="6" t="n">
+        <v>0.2143</v>
+      </c>
+      <c r="AH113" s="6" t="n">
+        <v>-0.07140000000000001</v>
+      </c>
+      <c r="AI113" s="6" t="n">
         <v>0.7</v>
+      </c>
+      <c r="AJ113" s="6" t="n">
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="114">
@@ -15906,13 +17282,25 @@
         <v>0</v>
       </c>
       <c r="AD114" s="6" t="n">
-        <v>0.3889</v>
+        <v>0</v>
       </c>
       <c r="AE114" s="6" t="n">
         <v>0.1189</v>
       </c>
       <c r="AF114" s="6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AG114" s="6" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="AH114" s="6" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="AI114" s="6" t="n">
         <v>0.875</v>
+      </c>
+      <c r="AJ114" s="6" t="n">
+        <v>0.1607</v>
       </c>
     </row>
     <row r="115">
@@ -16008,13 +17396,25 @@
         <v>0.0984</v>
       </c>
       <c r="AD115" s="6" t="n">
-        <v>0.4286</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="AE115" s="6" t="n">
         <v>0.0984</v>
       </c>
       <c r="AF115" s="6" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="AG115" s="6" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="AH115" s="6" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="AI115" s="6" t="n">
         <v>0.6364</v>
+      </c>
+      <c r="AJ115" s="6" t="n">
+        <v>-0.0779</v>
       </c>
     </row>
     <row r="116">
@@ -16114,6 +17514,10 @@
         <v>0</v>
       </c>
       <c r="AF116" s="6" t="n"/>
+      <c r="AG116" s="6" t="n"/>
+      <c r="AH116" s="6" t="n"/>
+      <c r="AI116" s="6" t="n"/>
+      <c r="AJ116" s="6" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -16208,13 +17612,25 @@
         <v>0.0813</v>
       </c>
       <c r="AD117" s="6" t="n">
-        <v>0.2286</v>
+        <v>0.0857</v>
       </c>
       <c r="AE117" s="6" t="n">
         <v>0.117</v>
       </c>
       <c r="AF117" s="6" t="n">
+        <v>0.1212</v>
+      </c>
+      <c r="AG117" s="6" t="n">
+        <v>0.2286</v>
+      </c>
+      <c r="AH117" s="6" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="AI117" s="6" t="n">
         <v>0.7272999999999999</v>
+      </c>
+      <c r="AJ117" s="6" t="n">
+        <v>-0.009599999999999999</v>
       </c>
     </row>
     <row r="118">
@@ -16310,13 +17726,25 @@
         <v>0</v>
       </c>
       <c r="AD118" s="6" t="n">
-        <v>0.2162</v>
+        <v>0</v>
       </c>
       <c r="AE118" s="6" t="n">
         <v>0.1398</v>
       </c>
       <c r="AF118" s="6" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="AG118" s="6" t="n">
+        <v>0.2162</v>
+      </c>
+      <c r="AH118" s="6" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="AI118" s="6" t="n">
         <v>0.7333</v>
+      </c>
+      <c r="AJ118" s="6" t="n">
+        <v>-0.0035</v>
       </c>
     </row>
     <row r="119">
@@ -16412,13 +17840,25 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="AD119" s="6" t="n">
-        <v>0.1935</v>
+        <v>0.0645</v>
       </c>
       <c r="AE119" s="6" t="n">
         <v>0.0354</v>
       </c>
       <c r="AF119" s="6" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="AG119" s="6" t="n">
+        <v>0.1935</v>
+      </c>
+      <c r="AH119" s="6" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="AI119" s="6" t="n">
         <v>0.6667</v>
+      </c>
+      <c r="AJ119" s="6" t="n">
+        <v>-0.0702</v>
       </c>
     </row>
     <row r="120">
@@ -16514,13 +17954,25 @@
         <v>0</v>
       </c>
       <c r="AD120" s="6" t="n">
-        <v>0.2143</v>
+        <v>0</v>
       </c>
       <c r="AE120" s="6" t="n">
         <v>0.2601</v>
       </c>
       <c r="AF120" s="6" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AG120" s="6" t="n">
+        <v>0.2143</v>
+      </c>
+      <c r="AH120" s="6" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="AI120" s="6" t="n">
         <v>0.7391</v>
+      </c>
+      <c r="AJ120" s="6" t="n">
+        <v>0.0023</v>
       </c>
     </row>
     <row r="121">
@@ -16620,6 +18072,10 @@
         <v>0.2315</v>
       </c>
       <c r="AF121" s="6" t="n"/>
+      <c r="AG121" s="6" t="n"/>
+      <c r="AH121" s="6" t="n"/>
+      <c r="AI121" s="6" t="n"/>
+      <c r="AJ121" s="6" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -16714,13 +18170,25 @@
         <v>0.1154</v>
       </c>
       <c r="AD122" s="6" t="n">
-        <v>0.2593</v>
+        <v>0.1111</v>
       </c>
       <c r="AE122" s="6" t="n">
         <v>0.2075</v>
       </c>
       <c r="AF122" s="6" t="n">
+        <v>0.1923</v>
+      </c>
+      <c r="AG122" s="6" t="n">
+        <v>0.2593</v>
+      </c>
+      <c r="AH122" s="6" t="n">
+        <v>0.0397</v>
+      </c>
+      <c r="AI122" s="6" t="n">
         <v>0.8077</v>
+      </c>
+      <c r="AJ122" s="6" t="n">
+        <v>0.0709</v>
       </c>
     </row>
     <row r="123">
@@ -16816,13 +18284,25 @@
         <v>0.0756</v>
       </c>
       <c r="AD123" s="6" t="n">
-        <v>0.2857</v>
+        <v>0.1429</v>
       </c>
       <c r="AE123" s="6" t="n">
         <v>0.08160000000000001</v>
       </c>
       <c r="AF123" s="6" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="AG123" s="6" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AH123" s="6" t="n">
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="AI123" s="6" t="n">
         <v>0.7692</v>
+      </c>
+      <c r="AJ123" s="6" t="n">
+        <v>0.0324</v>
       </c>
     </row>
     <row r="124">
@@ -16918,13 +18398,25 @@
         <v>0</v>
       </c>
       <c r="AD124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG124" s="6" t="n">
         <v>0.25</v>
       </c>
-      <c r="AE124" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF124" s="6" t="n">
-        <v>1</v>
+      <c r="AH124" s="6" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="AI124" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ124" s="6" t="n">
+        <v>0.2632</v>
       </c>
     </row>
     <row r="125">
@@ -17020,13 +18512,25 @@
         <v>0</v>
       </c>
       <c r="AD125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG125" s="6" t="n">
         <v>0.1786</v>
       </c>
-      <c r="AE125" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF125" s="6" t="n">
+      <c r="AH125" s="6" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AI125" s="6" t="n">
         <v>0.6538</v>
+      </c>
+      <c r="AJ125" s="6" t="n">
+        <v>-0.083</v>
       </c>
     </row>
     <row r="126">
@@ -17122,13 +18626,25 @@
         <v>0.0405</v>
       </c>
       <c r="AD126" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.0476</v>
       </c>
       <c r="AE126" s="6" t="n">
         <v>0.093</v>
       </c>
       <c r="AF126" s="6" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="AG126" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AH126" s="6" t="n">
+        <v>-0.0256</v>
+      </c>
+      <c r="AI126" s="6" t="n">
         <v>0.9545</v>
+      </c>
+      <c r="AJ126" s="6" t="n">
+        <v>-0.016</v>
       </c>
     </row>
     <row r="127">
@@ -17224,13 +18740,25 @@
         <v>0</v>
       </c>
       <c r="AD127" s="6" t="n">
-        <v>0.3478</v>
+        <v>0</v>
       </c>
       <c r="AE127" s="6" t="n">
         <v>0.0542</v>
       </c>
       <c r="AF127" s="6" t="n">
-        <v>1</v>
+        <v>0.05</v>
+      </c>
+      <c r="AG127" s="6" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AH127" s="6" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="AI127" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ127" s="6" t="n">
+        <v>0.0294</v>
       </c>
     </row>
     <row r="128">
@@ -17326,13 +18854,25 @@
         <v>0</v>
       </c>
       <c r="AD128" s="6" t="n">
-        <v>0.4286</v>
+        <v>0</v>
       </c>
       <c r="AE128" s="6" t="n">
         <v>0.2785</v>
       </c>
       <c r="AF128" s="6" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="AG128" s="6" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="AH128" s="6" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="AI128" s="6" t="n">
         <v>0.9444</v>
+      </c>
+      <c r="AJ128" s="6" t="n">
+        <v>-0.0261</v>
       </c>
     </row>
     <row r="129">
@@ -17428,13 +18968,25 @@
         <v>0.2456</v>
       </c>
       <c r="AD129" s="6" t="n">
-        <v>0.4211</v>
+        <v>0.2632</v>
       </c>
       <c r="AE129" s="6" t="n">
         <v>0.5071</v>
       </c>
       <c r="AF129" s="6" t="n">
+        <v>0.4737</v>
+      </c>
+      <c r="AG129" s="6" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="AH129" s="6" t="n">
+        <v>0.0621</v>
+      </c>
+      <c r="AI129" s="6" t="n">
         <v>0.9474</v>
+      </c>
+      <c r="AJ129" s="6" t="n">
+        <v>-0.0232</v>
       </c>
     </row>
     <row r="130">
@@ -17530,13 +19082,25 @@
         <v>0.2474</v>
       </c>
       <c r="AD130" s="6" t="n">
-        <v>0.375</v>
+        <v>0.2083</v>
       </c>
       <c r="AE130" s="6" t="n">
         <v>0.1703</v>
       </c>
       <c r="AF130" s="6" t="n">
-        <v>1</v>
+        <v>0.1765</v>
+      </c>
+      <c r="AG130" s="6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AH130" s="6" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AI130" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ130" s="6" t="n">
+        <v>0.0294</v>
       </c>
     </row>
     <row r="131">
@@ -17632,13 +19196,25 @@
         <v>0</v>
       </c>
       <c r="AD131" s="6" t="n">
-        <v>0.2857</v>
+        <v>0</v>
       </c>
       <c r="AE131" s="6" t="n">
         <v>0.1728</v>
       </c>
       <c r="AF131" s="6" t="n">
-        <v>1</v>
+        <v>0.1765</v>
+      </c>
+      <c r="AG131" s="6" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AH131" s="6" t="n">
+        <v>-0.0733</v>
+      </c>
+      <c r="AI131" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ131" s="6" t="n">
+        <v>0.0294</v>
       </c>
     </row>
     <row r="132">
@@ -17734,13 +19310,25 @@
         <v>0</v>
       </c>
       <c r="AD132" s="6" t="n">
-        <v>0.3684</v>
+        <v>0</v>
       </c>
       <c r="AE132" s="6" t="n">
         <v>0.188</v>
       </c>
       <c r="AF132" s="6" t="n">
-        <v>1</v>
+        <v>0.2</v>
+      </c>
+      <c r="AG132" s="6" t="n">
+        <v>0.3684</v>
+      </c>
+      <c r="AH132" s="6" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="AI132" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ132" s="6" t="n">
+        <v>0.0294</v>
       </c>
     </row>
     <row r="133">
@@ -17836,13 +19424,25 @@
         <v>0.1481</v>
       </c>
       <c r="AD133" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.1333</v>
       </c>
       <c r="AE133" s="6" t="n">
         <v>0.2548</v>
       </c>
       <c r="AF133" s="6" t="n">
-        <v>1</v>
+        <v>0.2308</v>
+      </c>
+      <c r="AG133" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AH133" s="6" t="n">
+        <v>-0.0256</v>
+      </c>
+      <c r="AI133" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ133" s="6" t="n">
+        <v>0.0294</v>
       </c>
     </row>
     <row r="134">
@@ -17938,13 +19538,25 @@
         <v>0</v>
       </c>
       <c r="AD134" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE134" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF134" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG134" s="6" t="n">
         <v>0.4167</v>
       </c>
-      <c r="AE134" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF134" s="6" t="n">
+      <c r="AH134" s="6" t="n">
+        <v>0.0577</v>
+      </c>
+      <c r="AI134" s="6" t="n">
         <v>0.9</v>
+      </c>
+      <c r="AJ134" s="6" t="n">
+        <v>-0.0706</v>
       </c>
     </row>
     <row r="135">
@@ -18040,13 +19652,25 @@
         <v>0</v>
       </c>
       <c r="AD135" s="6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AE135" s="6" t="n">
         <v>0.09619999999999999</v>
       </c>
       <c r="AF135" s="6" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="AG135" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH135" s="6" t="n">
+        <v>-0.159</v>
+      </c>
+      <c r="AI135" s="6" t="n">
         <v>0.9091</v>
+      </c>
+      <c r="AJ135" s="6" t="n">
+        <v>-0.0615</v>
       </c>
     </row>
     <row r="136">
@@ -18142,13 +19766,25 @@
         <v>0.1109</v>
       </c>
       <c r="AD136" s="6" t="n">
-        <v>0.375</v>
+        <v>0.125</v>
       </c>
       <c r="AE136" s="6" t="n">
         <v>0.3816</v>
       </c>
       <c r="AF136" s="6" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="AG136" s="6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AH136" s="6" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AI136" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ136" s="6" t="n">
+        <v>0.0294</v>
       </c>
     </row>
     <row r="137">
@@ -18244,13 +19880,25 @@
         <v>0</v>
       </c>
       <c r="AD137" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE137" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF137" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG137" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE137" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF137" s="6" t="n">
-        <v>1</v>
+      <c r="AH137" s="6" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="AI137" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ137" s="6" t="n">
+        <v>0.0294</v>
       </c>
     </row>
     <row r="138">
@@ -18346,13 +19994,25 @@
         <v>0.1099</v>
       </c>
       <c r="AD138" s="6" t="n">
-        <v>0.3514</v>
+        <v>0.1081</v>
       </c>
       <c r="AE138" s="6" t="n">
         <v>0.1856</v>
       </c>
       <c r="AF138" s="6" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="AG138" s="6" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="AH138" s="6" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="AI138" s="6" t="n">
         <v>0.6279</v>
+      </c>
+      <c r="AJ138" s="6" t="n">
+        <v>-0.0165</v>
       </c>
     </row>
     <row r="139">
@@ -18448,13 +20108,25 @@
         <v>0</v>
       </c>
       <c r="AD139" s="6" t="n">
-        <v>0.3056</v>
+        <v>0</v>
       </c>
       <c r="AE139" s="6" t="n">
         <v>0.0747</v>
       </c>
       <c r="AF139" s="6" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="AG139" s="6" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="AH139" s="6" t="n">
+        <v>-0.0365</v>
+      </c>
+      <c r="AI139" s="6" t="n">
         <v>0.6905</v>
+      </c>
+      <c r="AJ139" s="6" t="n">
+        <v>0.046</v>
       </c>
     </row>
     <row r="140">
@@ -18550,13 +20222,25 @@
         <v>0.1521</v>
       </c>
       <c r="AD140" s="6" t="n">
-        <v>0.4</v>
+        <v>0.1667</v>
       </c>
       <c r="AE140" s="6" t="n">
         <v>0.2055</v>
       </c>
       <c r="AF140" s="6" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="AG140" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH140" s="6" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="AI140" s="6" t="n">
         <v>0.6429</v>
+      </c>
+      <c r="AJ140" s="6" t="n">
+        <v>-0.0016</v>
       </c>
     </row>
     <row r="141">
@@ -18652,13 +20336,25 @@
         <v>0.0306</v>
       </c>
       <c r="AD141" s="6" t="n">
-        <v>0.3235</v>
+        <v>0.0294</v>
       </c>
       <c r="AE141" s="6" t="n">
         <v>0.1291</v>
       </c>
       <c r="AF141" s="6" t="n">
+        <v>0.1282</v>
+      </c>
+      <c r="AG141" s="6" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AH141" s="6" t="n">
+        <v>-0.0186</v>
+      </c>
+      <c r="AI141" s="6" t="n">
         <v>0.5897</v>
+      </c>
+      <c r="AJ141" s="6" t="n">
+        <v>-0.0547</v>
       </c>
     </row>
     <row r="142">
@@ -18754,13 +20450,25 @@
         <v>0.0399</v>
       </c>
       <c r="AD142" s="6" t="n">
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="AE142" s="6" t="n">
         <v>0.0674</v>
       </c>
       <c r="AF142" s="6" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="AG142" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH142" s="6" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="AI142" s="6" t="n">
         <v>0.6923</v>
+      </c>
+      <c r="AJ142" s="6" t="n">
+        <v>0.0479</v>
       </c>
     </row>
     <row r="143">
@@ -18856,13 +20564,25 @@
         <v>0.0473</v>
       </c>
       <c r="AD143" s="6" t="n">
-        <v>0.2857</v>
+        <v>0.0476</v>
       </c>
       <c r="AE143" s="6" t="n">
         <v>0.0399</v>
       </c>
       <c r="AF143" s="6" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="AG143" s="6" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AH143" s="6" t="n">
+        <v>-0.0564</v>
+      </c>
+      <c r="AI143" s="6" t="n">
         <v>0.7368</v>
+      </c>
+      <c r="AJ143" s="6" t="n">
+        <v>0.0924</v>
       </c>
     </row>
     <row r="144">
@@ -18958,13 +20678,25 @@
         <v>0.1264</v>
       </c>
       <c r="AD144" s="6" t="n">
-        <v>0.2857</v>
+        <v>0.1429</v>
       </c>
       <c r="AE144" s="6" t="n">
         <v>0.2134</v>
       </c>
       <c r="AF144" s="6" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="AG144" s="6" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AH144" s="6" t="n">
+        <v>-0.0564</v>
+      </c>
+      <c r="AI144" s="6" t="n">
         <v>0.5</v>
+      </c>
+      <c r="AJ144" s="6" t="n">
+        <v>-0.1444</v>
       </c>
     </row>
   </sheetData>
@@ -34978,7 +36710,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>R. REVUELTAS PAREJA</t>
+          <t>D. RYZINSKA</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
@@ -35006,7 +36738,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="8" t="n">
         <v>-4</v>
@@ -35032,7 +36764,7 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>D. RYZINSKA</t>
+          <t>R. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
@@ -35060,7 +36792,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="8" t="n">
         <v>-4</v>
@@ -35194,7 +36926,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>J. BALLESTER MANQUE</t>
+          <t>M. LÓPEZ MARTÍ</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -35248,7 +36980,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>B. GUAL CASTILLO</t>
+          <t>J. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -35264,7 +36996,7 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
@@ -35302,7 +37034,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>M. LÓPEZ MARTÍ</t>
+          <t>B. GUAL CASTILLO</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -35318,7 +37050,7 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -35572,7 +37304,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>M. PÉREZ CASTRO</t>
+          <t>V. MICHEL</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
@@ -35583,17 +37315,17 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H50" s="8" t="n">
@@ -35626,7 +37358,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>V. MICHEL</t>
+          <t>M. PÉREZ CASTRO</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
@@ -35637,7 +37369,7 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -35647,7 +37379,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H51" s="8" t="n">
